--- a/data/raw/김포 25년/항공통계상세조회(노선) (4).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (4).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10203</t>
-  </si>
-  <si>
-    <t>1817059</t>
-  </si>
-  <si>
-    <t>15750</t>
+    <t>5118</t>
+  </si>
+  <si>
+    <t>919136</t>
+  </si>
+  <si>
+    <t>7639</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,190 +53,175 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>72951</t>
-  </si>
-  <si>
-    <t>857</t>
+    <t>201</t>
+  </si>
+  <si>
+    <t>35559</t>
+  </si>
+  <si>
+    <t>451</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>6593</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>84342</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>3039</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>4869</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>81597</t>
+  </si>
+  <si>
+    <t>1750</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>11866</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>6298</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10460</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>8709</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>10218</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3351</t>
+  </si>
+  <si>
+    <t>621433</t>
+  </si>
+  <si>
+    <t>4249</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>6754</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>13240</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>167964</t>
-  </si>
-  <si>
-    <t>638</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>6434</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>9692</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>720</t>
-  </si>
-  <si>
-    <t>160054</t>
-  </si>
-  <si>
-    <t>2691</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>24164</t>
-  </si>
-  <si>
-    <t>260</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>12825</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20093</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>18388</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>21177</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6674</t>
-  </si>
-  <si>
-    <t>1222905</t>
-  </si>
-  <si>
-    <t>9633</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>12698</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>퉁치(TXN)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>3074</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>하노이(HAN)</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>50996</t>
-  </si>
-  <si>
-    <t>906</t>
+    <t>25778</t>
+  </si>
+  <si>
+    <t>305</t>
   </si>
 </sst>
 </file>
@@ -287,7 +272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -527,7 +512,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -538,16 +523,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>37</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -558,16 +543,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -578,16 +563,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -598,16 +583,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -618,56 +603,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s" s="0">
         <v>69</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
